--- a/reports/Debug-purgatory-20260105/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260105/For The Week Ending (Actual)_Visits.xlsx
@@ -448,7 +448,7 @@
         <v>46027</v>
       </c>
       <c r="C3" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>6</v>
@@ -462,10 +462,10 @@
         <v>46027</v>
       </c>
       <c r="C4" s="2">
-        <v>322</v>
+        <v>5</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,7 +476,7 @@
         <v>46027</v>
       </c>
       <c r="C5" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>6</v>
@@ -490,7 +490,7 @@
         <v>46027</v>
       </c>
       <c r="C6" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>6</v>
@@ -504,7 +504,7 @@
         <v>46027</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>6</v>
@@ -518,10 +518,10 @@
         <v>46027</v>
       </c>
       <c r="C8" s="2">
-        <v>1408</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,10 +532,10 @@
         <v>46027</v>
       </c>
       <c r="C9" s="2">
-        <v>48</v>
+        <v>322</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -560,7 +560,7 @@
         <v>46027</v>
       </c>
       <c r="C11" s="2">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>6</v>
@@ -574,10 +574,10 @@
         <v>46027</v>
       </c>
       <c r="C12" s="2">
-        <v>2</v>
+        <v>1407</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,7 +588,7 @@
         <v>46027</v>
       </c>
       <c r="C13" s="2">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>6</v>
